--- a/artfynd/A 49498-2025 artfynd.xlsx
+++ b/artfynd/A 49498-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133784372</v>
+        <v>133784353</v>
       </c>
       <c r="B13" t="n">
         <v>79978</v>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727124</v>
+        <v>727182</v>
       </c>
       <c r="R13" t="n">
-        <v>7170093</v>
+        <v>7170111</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,10 +2000,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133784392</v>
+        <v>133784396</v>
       </c>
       <c r="B14" t="n">
-        <v>80479</v>
+        <v>58839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2011,34 +2011,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>208249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>727018</v>
+        <v>726985</v>
       </c>
       <c r="R14" t="n">
-        <v>7170115</v>
+        <v>7170125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2080,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,6 +2098,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2107,7 +2117,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133784353</v>
+        <v>133784372</v>
       </c>
       <c r="B15" t="n">
         <v>79978</v>
@@ -2142,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>727182</v>
+        <v>727124</v>
       </c>
       <c r="R15" t="n">
-        <v>7170111</v>
+        <v>7170093</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2177,7 +2187,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2187,7 +2197,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2214,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133784396</v>
+        <v>133784392</v>
       </c>
       <c r="B16" t="n">
-        <v>58839</v>
+        <v>80479</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,43 +2235,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208249</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>726985</v>
+        <v>727018</v>
       </c>
       <c r="R16" t="n">
-        <v>7170125</v>
+        <v>7170115</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2294,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,7 +2304,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2312,7 +2313,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49498-2025 artfynd.xlsx
+++ b/artfynd/A 49498-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133784374</v>
       </c>
       <c r="B2" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133784354</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1009,45 +1009,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133784383</v>
+        <v>133784351</v>
       </c>
       <c r="B5" t="n">
-        <v>80478</v>
+        <v>58624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>103042</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727017</v>
+        <v>727199</v>
       </c>
       <c r="R5" t="n">
-        <v>7170131</v>
+        <v>7170109</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1097,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,53 +1129,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133784351</v>
+        <v>133784383</v>
       </c>
       <c r="B6" t="n">
-        <v>58624</v>
+        <v>80485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103042</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727199</v>
+        <v>727017</v>
       </c>
       <c r="R6" t="n">
-        <v>7170109</v>
+        <v>7170131</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1239,7 @@
         <v>133784360</v>
       </c>
       <c r="B7" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>133784386</v>
       </c>
       <c r="B8" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>133784395</v>
       </c>
       <c r="B9" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>133784382</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>133784389</v>
       </c>
       <c r="B11" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>133784390</v>
       </c>
       <c r="B12" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,10 +1893,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133784353</v>
+        <v>133784372</v>
       </c>
       <c r="B13" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727182</v>
+        <v>727124</v>
       </c>
       <c r="R13" t="n">
-        <v>7170111</v>
+        <v>7170093</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,54 +2000,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133784396</v>
+        <v>133784353</v>
       </c>
       <c r="B14" t="n">
-        <v>58839</v>
+        <v>79985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>726985</v>
+        <v>727182</v>
       </c>
       <c r="R14" t="n">
-        <v>7170125</v>
+        <v>7170111</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2070,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2080,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,7 +2089,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2117,45 +2107,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133784372</v>
+        <v>133784396</v>
       </c>
       <c r="B15" t="n">
-        <v>79978</v>
+        <v>58839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>208249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>727124</v>
+        <v>726985</v>
       </c>
       <c r="R15" t="n">
-        <v>7170093</v>
+        <v>7170125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2197,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,6 +2205,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>133784392</v>
       </c>
       <c r="B16" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>133784359</v>
       </c>
       <c r="B17" t="n">
-        <v>92013</v>
+        <v>92020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>133784387</v>
       </c>
       <c r="B19" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>133784380</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49498-2025 artfynd.xlsx
+++ b/artfynd/A 49498-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133784374</v>
+        <v>133784360</v>
       </c>
       <c r="B2" t="n">
-        <v>79366</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727120</v>
+        <v>727168</v>
       </c>
       <c r="R2" t="n">
-        <v>7170153</v>
+        <v>7170101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133784354</v>
+        <v>133784366</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727185</v>
+        <v>727131</v>
       </c>
       <c r="R3" t="n">
-        <v>7170118</v>
+        <v>7170073</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133784400</v>
+        <v>133784359</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>92027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,42 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727010</v>
+        <v>727164</v>
       </c>
       <c r="R4" t="n">
-        <v>7170055</v>
+        <v>7170110</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,19 +969,14 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Uppfläkta barkfläckar på basen av gamla granar. Svårt att artbestämma säkert, samt bedöma ålder</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1009,53 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133784351</v>
+        <v>133784393</v>
       </c>
       <c r="B5" t="n">
-        <v>58624</v>
+        <v>96410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103042</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727199</v>
+        <v>727018</v>
       </c>
       <c r="R5" t="n">
-        <v>7170109</v>
+        <v>7170115</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133784383</v>
+        <v>133784399</v>
       </c>
       <c r="B6" t="n">
-        <v>80485</v>
+        <v>96410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727017</v>
+        <v>726989</v>
       </c>
       <c r="R6" t="n">
-        <v>7170131</v>
+        <v>7170041</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133784360</v>
+        <v>133784346</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>727168</v>
+        <v>727295</v>
       </c>
       <c r="R7" t="n">
-        <v>7170101</v>
+        <v>7170114</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133784386</v>
+        <v>133784348</v>
       </c>
       <c r="B8" t="n">
-        <v>80481</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727021</v>
+        <v>727224</v>
       </c>
       <c r="R8" t="n">
-        <v>7170130</v>
+        <v>7170092</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,12 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Foto 1</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133784395</v>
+        <v>133784354</v>
       </c>
       <c r="B9" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>727008</v>
+        <v>727185</v>
       </c>
       <c r="R9" t="n">
-        <v>7170100</v>
+        <v>7170118</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Foto 1</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133784382</v>
+        <v>133784374</v>
       </c>
       <c r="B10" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>727049</v>
+        <v>727120</v>
       </c>
       <c r="R10" t="n">
-        <v>7170135</v>
+        <v>7170153</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133784389</v>
+        <v>133784380</v>
       </c>
       <c r="B11" t="n">
-        <v>80481</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>727011</v>
+        <v>727037</v>
       </c>
       <c r="R11" t="n">
-        <v>7170125</v>
+        <v>7170128</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,12 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Foto 2</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133784390</v>
+        <v>133784479</v>
       </c>
       <c r="B12" t="n">
-        <v>80481</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1821,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>727017</v>
+        <v>727306</v>
       </c>
       <c r="R12" t="n">
-        <v>7170126</v>
+        <v>7170179</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1856,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1866,7 +1825,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Flera bålar flera träd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133784372</v>
+        <v>133784382</v>
       </c>
       <c r="B13" t="n">
-        <v>79985</v>
+        <v>79130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1928,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727124</v>
+        <v>727049</v>
       </c>
       <c r="R13" t="n">
-        <v>7170093</v>
+        <v>7170135</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,7 +1967,7 @@
         <v>133784353</v>
       </c>
       <c r="B14" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,54 +2071,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133784396</v>
+        <v>133784364</v>
       </c>
       <c r="B15" t="n">
-        <v>58839</v>
+        <v>79992</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208249</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>726985</v>
+        <v>727143</v>
       </c>
       <c r="R15" t="n">
-        <v>7170125</v>
+        <v>7170075</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,7 +2160,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2224,32 +2178,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133784392</v>
+        <v>133784365</v>
       </c>
       <c r="B16" t="n">
-        <v>80486</v>
+        <v>79992</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2259,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>727018</v>
+        <v>727127</v>
       </c>
       <c r="R16" t="n">
-        <v>7170115</v>
+        <v>7170081</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2304,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2331,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133784359</v>
+        <v>133784371</v>
       </c>
       <c r="B17" t="n">
-        <v>92020</v>
+        <v>79992</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2342,21 +2296,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2366,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>727164</v>
+        <v>727126</v>
       </c>
       <c r="R17" t="n">
-        <v>7170110</v>
+        <v>7170061</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2411,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,53 +2392,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133784376</v>
+        <v>133784372</v>
       </c>
       <c r="B18" t="n">
-        <v>58624</v>
+        <v>79992</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103042</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>727057</v>
+        <v>727124</v>
       </c>
       <c r="R18" t="n">
-        <v>7170138</v>
+        <v>7170093</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2516,7 +2462,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2526,7 +2472,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,32 +2499,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133784387</v>
+        <v>133784386</v>
       </c>
       <c r="B19" t="n">
-        <v>80486</v>
+        <v>80488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2634,6 +2580,11 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Foto 1</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133784380</v>
+        <v>133784389</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>80488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2671,21 +2622,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2695,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>727037</v>
+        <v>727011</v>
       </c>
       <c r="R20" t="n">
-        <v>7170128</v>
+        <v>7170125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2740,7 +2691,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Foto 2</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,6 +2720,1454 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133784390</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>727017</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7170126</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133784383</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80492</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>727017</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7170131</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133784387</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>727021</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7170130</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133784392</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>727018</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7170115</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133784400</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>727010</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7170055</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Uppfläkta barkfläckar på basen av gamla granar. Svårt att artbestämma säkert, samt bedöma ålder</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133784351</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58624</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>727199</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7170109</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133784376</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58624</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>727057</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7170138</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133784368</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>727132</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7170063</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133784396</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>726985</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7170125</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133784395</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>727008</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7170100</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Foto 1</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133784350</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>727222</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7170091</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133784363</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>727161</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7170095</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133784357</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>727185</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7170118</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49498-2025 artfynd.xlsx
+++ b/artfynd/A 49498-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784360</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784366</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784359</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784393</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784399</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784346</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784348</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784354</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784374</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784380</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784479</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784382</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784353</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784364</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784365</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2389,6 +2469,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784371</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2496,6 +2581,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784372</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2608,6 +2698,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784386</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2720,6 +2815,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784389</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2827,6 +2927,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784390</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2934,6 +3039,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784383</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3041,6 +3151,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784387</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3148,6 +3263,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784392</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3268,6 +3388,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784400</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3388,6 +3513,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784351</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3503,6 +3633,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784376</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3618,6 +3753,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784368</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3735,6 +3875,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784396</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3847,6 +3992,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784395</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3954,6 +4104,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784350</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4061,6 +4216,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784363</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4168,8 +4328,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784357</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>